--- a/forms/trg/Formulir_TRG_climatebmd.xlsx
+++ b/forms/trg/Formulir_TRG_climatebmd.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,20 +925,24 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ilham Alimuddin</t>
+          <t>Halmar Halide, PhD</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Geology Department, Faculty of Engineering Universitas Hasanuddin</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Hydrometeorology Laboratory, Geophysics Dept. FMIPA Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Hydrometeorology, modeling climate-based phenomena, with a focus on a wide range of topics, from tropical cyclones to infectious diseases. My work encompasses a spectrum of modeling techniques, from simple statistical methods to advanced machine learning algorithms. The outputs of my models are designed to provide diverse users with valuable climate-based information, empowering them to make informed decisions in their respective fields</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -958,17 +962,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. M. Ivan Azis</t>
+          <t>Dr. Ilham Alimuddin</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Mathematic Department, FMIPA Hasanuddin University</t>
+          <t>Geology Department, Faculty of Engineering Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -991,17 +995,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Yadi Mulyadi</t>
+          <t>Prof. M. Ivan Azis</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Archaeology Department, Faculty of Cultural Science, Hanuddin University</t>
+          <t>Mathematic Department, FMIPA Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="n"/>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nur Haedar, M.Si</t>
+          <t>Dr. Yadi Mulyadi</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Biology Department FMIPA Hasanuddin University</t>
+          <t>Archaeology Department, Faculty of Cultural Science, Hanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1057,17 +1061,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. K. Kimbrough</t>
+          <t>Dr. Nur Haedar, M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Associate Research Fellow for the Faculty of Science at the Univ. Wollongong, Australia</t>
+          <t>Biology Department FMIPA Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1090,20 +1094,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Joelle I. Rosser MD</t>
+          <t>Dr. A. K. Kimbrough</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Medicine (Infectious Disease) at Stanford Univ, USA.</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Associate Research Fellow for the Faculty of Science at the Univ. Wollongong, Australia</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1123,18 +1127,18 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Rustan Lebe, M.Hum</t>
+          <t>Joelle I. Rosser MD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>manage the Fort Rotterdam Site, Leang-Leang Archaeological Park, and Leang Timpuseng.</t>
+          <t>Medicine (Infectious Disease) at Stanford Univ, USA.</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1156,20 +1160,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andika, S.Si., M.Si</t>
+          <t>Rustan Lebe, M.Hum</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Geophysics Dept FMIPA Hanuddin University</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>manage the Fort Rotterdam Site, Leang-Leang Archaeological Park, and Leang Timpuseng.</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1187,9 +1191,21 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Andika, S.Si., M.Si</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Geophysics Dept FMIPA Hanuddin University</t>
+        </is>
+      </c>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1198,7 +1214,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1387,15 +1407,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
